--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2024.xlsx
@@ -73,12 +73,6 @@
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
@@ -91,12 +85,6 @@
     <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
@@ -874,6 +862,12 @@
     <t xml:space="preserve">La Ligua</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">7201</t>
   </si>
   <si>
@@ -1366,6 +1360,12 @@
     <t xml:space="preserve">Los Vilos</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4202</t>
   </si>
   <si>
@@ -2059,7 +2059,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:27</t>
+    <t xml:space="preserve">2026-09-09 20:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2603,7 +2603,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>15</v>
@@ -2635,7 +2635,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4.52</v>
+        <v>4.25</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>15</v>
@@ -2667,7 +2667,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4.25</v>
+        <v>3.73</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>15</v>
@@ -2678,16 +2678,16 @@
         <v>2024</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2699,7 +2699,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3.81</v>
+        <v>3.07</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2710,16 +2710,16 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -2731,7 +2731,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3.73</v>
+        <v>2.25</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2745,7 +2745,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>29</v>
@@ -2763,7 +2763,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3.07</v>
+        <v>2.09</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2774,10 +2774,10 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>31</v>
@@ -2795,7 +2795,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2806,10 +2806,10 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>33</v>
@@ -2827,7 +2827,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2.09</v>
+        <v>1.54</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2838,10 +2838,10 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.08</v>
+        <v>1.46</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2870,10 +2870,10 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>37</v>
@@ -2891,7 +2891,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.54</v>
+        <v>0.69</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2902,28 +2902,28 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.46</v>
+        <v>4.47</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -2934,28 +2934,28 @@
         <v>2024</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.69</v>
+        <v>4.34</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -2966,28 +2966,28 @@
         <v>2024</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4.47</v>
+        <v>4.25</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -2998,28 +2998,28 @@
         <v>2024</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3030,28 +3030,28 @@
         <v>2024</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3062,28 +3062,28 @@
         <v>2024</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3094,28 +3094,28 @@
         <v>2024</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4.08</v>
+        <v>3.79</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3126,28 +3126,28 @@
         <v>2024</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3.82</v>
+        <v>3.69</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3158,10 +3158,10 @@
         <v>2024</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>61</v>
@@ -3170,16 +3170,16 @@
         <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3190,10 +3190,10 @@
         <v>2024</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>63</v>
@@ -3202,16 +3202,16 @@
         <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3222,10 +3222,10 @@
         <v>2024</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>65</v>
@@ -3234,16 +3234,16 @@
         <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3254,10 +3254,10 @@
         <v>2024</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
@@ -3266,16 +3266,16 @@
         <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3286,10 +3286,10 @@
         <v>2024</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>69</v>
@@ -3298,16 +3298,16 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3318,10 +3318,10 @@
         <v>2024</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -3330,16 +3330,16 @@
         <v>72</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3350,10 +3350,10 @@
         <v>2024</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>73</v>
@@ -3362,16 +3362,16 @@
         <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3385,7 +3385,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3394,16 +3394,16 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3414,10 +3414,10 @@
         <v>2024</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3426,16 +3426,16 @@
         <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3449,7 +3449,7 @@
         <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3458,16 +3458,16 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3478,10 +3478,10 @@
         <v>2024</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3490,16 +3490,16 @@
         <v>82</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3510,10 +3510,10 @@
         <v>2024</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3522,16 +3522,16 @@
         <v>84</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3545,7 +3545,7 @@
         <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>85</v>
@@ -3554,16 +3554,16 @@
         <v>86</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3574,10 +3574,10 @@
         <v>2024</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3586,16 +3586,16 @@
         <v>88</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3609,7 +3609,7 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>89</v>
@@ -3618,16 +3618,16 @@
         <v>90</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3638,10 +3638,10 @@
         <v>2024</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>91</v>
@@ -3650,16 +3650,16 @@
         <v>92</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3673,7 +3673,7 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>93</v>
@@ -3682,16 +3682,16 @@
         <v>94</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3702,10 +3702,10 @@
         <v>2024</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
@@ -3714,16 +3714,16 @@
         <v>96</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3734,10 +3734,10 @@
         <v>2024</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>97</v>
@@ -3746,16 +3746,16 @@
         <v>98</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3766,10 +3766,10 @@
         <v>2024</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>99</v>
@@ -3778,16 +3778,16 @@
         <v>100</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3798,10 +3798,10 @@
         <v>2024</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>101</v>
@@ -3810,16 +3810,16 @@
         <v>102</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3833,7 +3833,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3842,16 +3842,16 @@
         <v>104</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3862,10 +3862,10 @@
         <v>2024</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>105</v>
@@ -3874,16 +3874,16 @@
         <v>106</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3894,10 +3894,10 @@
         <v>2024</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -3906,16 +3906,16 @@
         <v>108</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -3926,10 +3926,10 @@
         <v>2024</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>109</v>
@@ -3938,16 +3938,16 @@
         <v>110</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -3961,7 +3961,7 @@
         <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>111</v>
@@ -3970,16 +3970,16 @@
         <v>112</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -3990,10 +3990,10 @@
         <v>2024</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>113</v>
@@ -4002,16 +4002,16 @@
         <v>114</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4022,10 +4022,10 @@
         <v>2024</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4034,16 +4034,16 @@
         <v>116</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4054,10 +4054,10 @@
         <v>2024</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>117</v>
@@ -4066,16 +4066,16 @@
         <v>118</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -4086,10 +4086,10 @@
         <v>2024</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4098,16 +4098,16 @@
         <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -4118,10 +4118,10 @@
         <v>2024</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4130,16 +4130,16 @@
         <v>122</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4150,10 +4150,10 @@
         <v>2024</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4162,16 +4162,16 @@
         <v>124</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4182,10 +4182,10 @@
         <v>2024</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4194,10 +4194,10 @@
         <v>126</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4214,10 +4214,10 @@
         <v>2024</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4226,16 +4226,16 @@
         <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -4246,10 +4246,10 @@
         <v>2024</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4258,16 +4258,16 @@
         <v>130</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4281,7 +4281,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4290,16 +4290,16 @@
         <v>132</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4313,7 +4313,7 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4322,16 +4322,16 @@
         <v>134</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4342,10 +4342,10 @@
         <v>2024</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4354,16 +4354,16 @@
         <v>136</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4374,22 +4374,22 @@
         <v>2024</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4409,25 +4409,25 @@
         <v>13</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4438,10 +4438,10 @@
         <v>2024</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4450,16 +4450,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4470,10 +4470,10 @@
         <v>2024</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4482,16 +4482,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4502,10 +4502,10 @@
         <v>2024</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4514,16 +4514,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4534,10 +4534,10 @@
         <v>2024</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4546,16 +4546,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4569,7 +4569,7 @@
         <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4578,16 +4578,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4601,7 +4601,7 @@
         <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4610,16 +4610,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4630,10 +4630,10 @@
         <v>2024</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4642,16 +4642,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4662,10 +4662,10 @@
         <v>2024</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4674,16 +4674,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4694,10 +4694,10 @@
         <v>2024</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4706,16 +4706,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4726,10 +4726,10 @@
         <v>2024</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4738,16 +4738,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4758,10 +4758,10 @@
         <v>2024</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4770,16 +4770,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4790,10 +4790,10 @@
         <v>2024</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4802,16 +4802,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4822,10 +4822,10 @@
         <v>2024</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4834,16 +4834,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4854,10 +4854,10 @@
         <v>2024</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4866,16 +4866,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4886,10 +4886,10 @@
         <v>2024</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4898,10 +4898,10 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4918,10 +4918,10 @@
         <v>2024</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4930,16 +4930,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -4950,10 +4950,10 @@
         <v>2024</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -4962,16 +4962,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -4982,10 +4982,10 @@
         <v>2024</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -4994,16 +4994,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -5017,7 +5017,7 @@
         <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5026,16 +5026,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5046,10 +5046,10 @@
         <v>2024</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5058,16 +5058,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5078,10 +5078,10 @@
         <v>2024</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5090,16 +5090,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -5110,10 +5110,10 @@
         <v>2024</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5122,16 +5122,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5142,10 +5142,10 @@
         <v>2024</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5154,16 +5154,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5174,10 +5174,10 @@
         <v>2024</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5186,16 +5186,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -5206,10 +5206,10 @@
         <v>2024</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5218,16 +5218,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -5238,10 +5238,10 @@
         <v>2024</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5250,16 +5250,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -5270,10 +5270,10 @@
         <v>2024</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5282,16 +5282,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -5302,10 +5302,10 @@
         <v>2024</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5314,16 +5314,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5334,10 +5334,10 @@
         <v>2024</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5346,16 +5346,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -5366,10 +5366,10 @@
         <v>2024</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5378,16 +5378,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -5398,10 +5398,10 @@
         <v>2024</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5410,10 +5410,10 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5430,10 +5430,10 @@
         <v>2024</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5442,10 +5442,10 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5462,10 +5462,10 @@
         <v>2024</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5474,16 +5474,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5494,10 +5494,10 @@
         <v>2024</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5506,16 +5506,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5526,10 +5526,10 @@
         <v>2024</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5538,16 +5538,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5558,10 +5558,10 @@
         <v>2024</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5570,16 +5570,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5593,7 +5593,7 @@
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5602,16 +5602,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5622,10 +5622,10 @@
         <v>2024</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5634,16 +5634,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5654,10 +5654,10 @@
         <v>2024</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5666,16 +5666,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5686,10 +5686,10 @@
         <v>2024</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5698,16 +5698,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5718,10 +5718,10 @@
         <v>2024</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5730,16 +5730,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5750,10 +5750,10 @@
         <v>2024</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5762,16 +5762,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5782,10 +5782,10 @@
         <v>2024</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5794,16 +5794,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5817,7 +5817,7 @@
         <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5826,16 +5826,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5846,10 +5846,10 @@
         <v>2024</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5858,16 +5858,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5881,7 +5881,7 @@
         <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5890,16 +5890,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5910,10 +5910,10 @@
         <v>2024</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5922,16 +5922,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -5942,10 +5942,10 @@
         <v>2024</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -5954,16 +5954,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -5974,10 +5974,10 @@
         <v>2024</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -5986,16 +5986,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -6009,7 +6009,7 @@
         <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6018,16 +6018,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -6038,10 +6038,10 @@
         <v>2024</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6050,16 +6050,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -6070,10 +6070,10 @@
         <v>2024</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6082,16 +6082,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6102,10 +6102,10 @@
         <v>2024</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6114,16 +6114,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>15</v>
@@ -6137,7 +6137,7 @@
         <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6146,16 +6146,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>15</v>
@@ -6169,7 +6169,7 @@
         <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6178,16 +6178,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6198,10 +6198,10 @@
         <v>2024</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6210,16 +6210,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -6230,10 +6230,10 @@
         <v>2024</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6242,16 +6242,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6262,10 +6262,10 @@
         <v>2024</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6274,10 +6274,10 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6294,10 +6294,10 @@
         <v>2024</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6306,16 +6306,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6326,10 +6326,10 @@
         <v>2024</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6338,16 +6338,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -6361,7 +6361,7 @@
         <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6370,16 +6370,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6390,10 +6390,10 @@
         <v>2024</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6402,16 +6402,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6422,28 +6422,28 @@
         <v>2024</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>267</v>
+        <v>56</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6454,28 +6454,28 @@
         <v>2024</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D125" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="F125" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6486,28 +6486,28 @@
         <v>2024</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D126" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F126" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6518,10 +6518,10 @@
         <v>2024</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>271</v>
@@ -6530,16 +6530,16 @@
         <v>272</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6550,10 +6550,10 @@
         <v>2024</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>273</v>
@@ -6562,16 +6562,16 @@
         <v>274</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6582,10 +6582,10 @@
         <v>2024</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>275</v>
@@ -6594,16 +6594,16 @@
         <v>276</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6614,10 +6614,10 @@
         <v>2024</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>277</v>
@@ -6626,16 +6626,16 @@
         <v>278</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6649,7 +6649,7 @@
         <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>279</v>
@@ -6658,16 +6658,16 @@
         <v>280</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6681,7 +6681,7 @@
         <v>6</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6690,16 +6690,16 @@
         <v>282</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6710,10 +6710,10 @@
         <v>2024</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>283</v>
@@ -6722,10 +6722,10 @@
         <v>284</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6742,10 +6742,10 @@
         <v>2024</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>285</v>
@@ -6754,16 +6754,16 @@
         <v>286</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6774,10 +6774,10 @@
         <v>2024</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6786,16 +6786,16 @@
         <v>288</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>15</v>
@@ -6806,10 +6806,10 @@
         <v>2024</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6818,16 +6818,16 @@
         <v>290</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6838,10 +6838,10 @@
         <v>2024</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>291</v>
@@ -6850,10 +6850,10 @@
         <v>292</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6870,10 +6870,10 @@
         <v>2024</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>293</v>
@@ -6882,16 +6882,16 @@
         <v>294</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6902,10 +6902,10 @@
         <v>2024</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>295</v>
@@ -6914,16 +6914,16 @@
         <v>296</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -6934,10 +6934,10 @@
         <v>2024</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>297</v>
@@ -6946,10 +6946,10 @@
         <v>298</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -6966,10 +6966,10 @@
         <v>2024</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -6978,16 +6978,16 @@
         <v>300</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -7001,7 +7001,7 @@
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7010,10 +7010,10 @@
         <v>302</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7030,10 +7030,10 @@
         <v>2024</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7042,16 +7042,16 @@
         <v>304</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7062,10 +7062,10 @@
         <v>2024</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7074,10 +7074,10 @@
         <v>306</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7094,10 +7094,10 @@
         <v>2024</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7106,10 +7106,10 @@
         <v>308</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7126,10 +7126,10 @@
         <v>2024</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7138,10 +7138,10 @@
         <v>310</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7158,10 +7158,10 @@
         <v>2024</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7170,16 +7170,16 @@
         <v>312</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7190,10 +7190,10 @@
         <v>2024</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>313</v>
@@ -7202,16 +7202,16 @@
         <v>314</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -7222,10 +7222,10 @@
         <v>2024</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7234,16 +7234,16 @@
         <v>316</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7254,10 +7254,10 @@
         <v>2024</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7266,16 +7266,16 @@
         <v>318</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -7286,10 +7286,10 @@
         <v>2024</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7298,16 +7298,16 @@
         <v>320</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>15</v>
@@ -7318,10 +7318,10 @@
         <v>2024</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7330,16 +7330,16 @@
         <v>322</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -7350,10 +7350,10 @@
         <v>2024</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7362,10 +7362,10 @@
         <v>324</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7382,10 +7382,10 @@
         <v>2024</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7394,16 +7394,16 @@
         <v>326</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>15</v>
@@ -7414,10 +7414,10 @@
         <v>2024</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7426,16 +7426,16 @@
         <v>328</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7446,10 +7446,10 @@
         <v>2024</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7458,10 +7458,10 @@
         <v>330</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7478,10 +7478,10 @@
         <v>2024</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>331</v>
@@ -7490,16 +7490,16 @@
         <v>332</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>15</v>
@@ -7510,10 +7510,10 @@
         <v>2024</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>333</v>
@@ -7522,16 +7522,16 @@
         <v>334</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7542,10 +7542,10 @@
         <v>2024</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>335</v>
@@ -7554,10 +7554,10 @@
         <v>336</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7574,10 +7574,10 @@
         <v>2024</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7586,16 +7586,16 @@
         <v>338</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7606,10 +7606,10 @@
         <v>2024</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7618,16 +7618,16 @@
         <v>340</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7638,10 +7638,10 @@
         <v>2024</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7650,16 +7650,16 @@
         <v>342</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7670,10 +7670,10 @@
         <v>2024</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7682,10 +7682,10 @@
         <v>344</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7705,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7714,16 +7714,16 @@
         <v>346</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7734,10 +7734,10 @@
         <v>2024</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7746,16 +7746,16 @@
         <v>348</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7766,10 +7766,10 @@
         <v>2024</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7778,16 +7778,16 @@
         <v>350</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7801,7 +7801,7 @@
         <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7810,16 +7810,16 @@
         <v>352</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7830,10 +7830,10 @@
         <v>2024</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7842,16 +7842,16 @@
         <v>354</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7862,10 +7862,10 @@
         <v>2024</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7874,16 +7874,16 @@
         <v>356</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7894,10 +7894,10 @@
         <v>2024</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -7906,10 +7906,10 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7926,10 +7926,10 @@
         <v>2024</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -7938,16 +7938,16 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -7958,10 +7958,10 @@
         <v>2024</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -7970,10 +7970,10 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -7990,10 +7990,10 @@
         <v>2024</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8002,16 +8002,16 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>15</v>
@@ -8022,10 +8022,10 @@
         <v>2024</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8034,16 +8034,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8054,10 +8054,10 @@
         <v>2024</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8066,16 +8066,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8086,10 +8086,10 @@
         <v>2024</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8098,16 +8098,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8121,7 +8121,7 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8130,16 +8130,16 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -8150,10 +8150,10 @@
         <v>2024</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8162,16 +8162,16 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -8185,7 +8185,7 @@
         <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8194,16 +8194,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8214,10 +8214,10 @@
         <v>2024</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8226,16 +8226,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8246,28 +8246,28 @@
         <v>2024</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>43</v>
+        <v>379</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>46</v>
+        <v>382</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>47</v>
+        <v>383</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>0.64</v>
+        <v>5.06</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8278,28 +8278,28 @@
         <v>2024</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D182" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="E182" s="2" t="s">
+      <c r="G182" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="F182" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>5.06</v>
+        <v>4.67</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8310,28 +8310,28 @@
         <v>2024</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>4.67</v>
+        <v>4.28</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -8342,10 +8342,10 @@
         <v>2024</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>390</v>
@@ -8354,16 +8354,16 @@
         <v>391</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>4.28</v>
+        <v>4.07</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8374,10 +8374,10 @@
         <v>2024</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>392</v>
@@ -8386,16 +8386,16 @@
         <v>393</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>4.07</v>
+        <v>3.87</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8406,28 +8406,28 @@
         <v>2024</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>3.87</v>
+        <v>3.46</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8438,10 +8438,10 @@
         <v>2024</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>397</v>
@@ -8450,16 +8450,16 @@
         <v>398</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8473,7 +8473,7 @@
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>399</v>
@@ -8482,16 +8482,16 @@
         <v>400</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8502,10 +8502,10 @@
         <v>2024</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>401</v>
@@ -8514,16 +8514,16 @@
         <v>402</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8537,7 +8537,7 @@
         <v>1</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>403</v>
@@ -8546,16 +8546,16 @@
         <v>404</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8566,10 +8566,10 @@
         <v>2024</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>405</v>
@@ -8578,10 +8578,10 @@
         <v>406</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8601,25 +8601,25 @@
         <v>2</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>407</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8630,28 +8630,28 @@
         <v>2024</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="E193" s="2" t="s">
-        <v>396</v>
-      </c>
       <c r="F193" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8665,7 +8665,7 @@
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>410</v>
@@ -8674,16 +8674,16 @@
         <v>411</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8694,10 +8694,10 @@
         <v>2024</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>412</v>
@@ -8706,16 +8706,16 @@
         <v>413</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8726,10 +8726,10 @@
         <v>2024</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>414</v>
@@ -8738,16 +8738,16 @@
         <v>415</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8758,10 +8758,10 @@
         <v>2024</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>416</v>
@@ -8770,16 +8770,16 @@
         <v>417</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8790,10 +8790,10 @@
         <v>2024</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>418</v>
@@ -8802,16 +8802,16 @@
         <v>419</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8822,10 +8822,10 @@
         <v>2024</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>420</v>
@@ -8834,16 +8834,16 @@
         <v>421</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8857,25 +8857,25 @@
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>422</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>423</v>
+        <v>384</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8889,19 +8889,19 @@
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D201" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="E201" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="F201" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8921,7 +8921,7 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>425</v>
@@ -8930,16 +8930,16 @@
         <v>426</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -8953,7 +8953,7 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>427</v>
@@ -8962,16 +8962,16 @@
         <v>428</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -8982,10 +8982,10 @@
         <v>2024</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>429</v>
@@ -8994,16 +8994,16 @@
         <v>430</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9014,10 +9014,10 @@
         <v>2024</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>431</v>
@@ -9026,16 +9026,16 @@
         <v>432</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -9046,10 +9046,10 @@
         <v>2024</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>433</v>
@@ -9058,16 +9058,16 @@
         <v>434</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -9078,10 +9078,10 @@
         <v>2024</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>435</v>
@@ -9090,10 +9090,10 @@
         <v>436</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9110,10 +9110,10 @@
         <v>2024</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>437</v>
@@ -9122,16 +9122,16 @@
         <v>438</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>15</v>
@@ -9142,10 +9142,10 @@
         <v>2024</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>439</v>
@@ -9154,10 +9154,10 @@
         <v>440</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9177,7 +9177,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>441</v>
@@ -9186,16 +9186,16 @@
         <v>442</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>15</v>
@@ -9209,7 +9209,7 @@
         <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>443</v>
@@ -9218,16 +9218,16 @@
         <v>444</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>15</v>
@@ -9238,10 +9238,10 @@
         <v>2024</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>445</v>
@@ -9250,16 +9250,16 @@
         <v>446</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>15</v>
@@ -9273,7 +9273,7 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>447</v>
@@ -9282,16 +9282,16 @@
         <v>448</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>15</v>
@@ -9305,7 +9305,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>449</v>
@@ -9314,10 +9314,10 @@
         <v>450</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9337,7 +9337,7 @@
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>451</v>
@@ -9346,10 +9346,10 @@
         <v>452</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9369,7 +9369,7 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>453</v>
@@ -9378,10 +9378,10 @@
         <v>454</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9401,7 +9401,7 @@
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>455</v>
@@ -9410,10 +9410,10 @@
         <v>456</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9433,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>457</v>
@@ -9442,10 +9442,10 @@
         <v>458</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9465,7 +9465,7 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>459</v>
@@ -9474,10 +9474,10 @@
         <v>460</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2024.xlsx
@@ -358,18 +358,18 @@
     <t xml:space="preserve">San Bernardo</t>
   </si>
   <si>
+    <t xml:space="preserve">6109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
     <t xml:space="preserve">6303</t>
   </si>
   <si>
     <t xml:space="preserve">Chimbarongo</t>
   </si>
   <si>
-    <t xml:space="preserve">6109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
     <t xml:space="preserve">5605</t>
   </si>
   <si>
@@ -388,18 +388,18 @@
     <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
+    <t xml:space="preserve">6101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rancagua</t>
+  </si>
+  <si>
     <t xml:space="preserve">6111</t>
   </si>
   <si>
     <t xml:space="preserve">Olivar</t>
   </si>
   <si>
-    <t xml:space="preserve">6101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rancagua</t>
-  </si>
-  <si>
     <t xml:space="preserve">5801</t>
   </si>
   <si>
@@ -661,18 +661,18 @@
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
+    <t xml:space="preserve">7101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talca</t>
+  </si>
+  <si>
     <t xml:space="preserve">7104</t>
   </si>
   <si>
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
-    <t xml:space="preserve">7101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talca</t>
-  </si>
-  <si>
     <t xml:space="preserve">5102</t>
   </si>
   <si>
@@ -916,18 +916,18 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
+    <t xml:space="preserve">13505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
     <t xml:space="preserve">13605</t>
   </si>
   <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">13505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
     <t xml:space="preserve">5405</t>
   </si>
   <si>
@@ -2059,7 +2059,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:20</t>
+    <t xml:space="preserve">2026-09-18 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2024.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="698">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">metric_label</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11303</t>
@@ -76,9 +76,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
@@ -148,7 +145,7 @@
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5107</t>
@@ -265,9 +262,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">13103</t>
   </si>
   <si>
@@ -442,7 +436,7 @@
     <t xml:space="preserve">Paine</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16304</t>
@@ -1168,7 +1162,7 @@
     <t xml:space="preserve">Petorca</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1403</t>
@@ -1414,7 +1408,7 @@
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8314</t>
@@ -1450,7 +1444,7 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9113</t>
@@ -1483,7 +1477,7 @@
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14105</t>
@@ -1747,7 +1741,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">8203</t>
@@ -1885,7 +1879,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">14104</t>
@@ -2071,7 +2065,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:31</t>
+    <t xml:space="preserve">2026-10-05 18:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2603,7 +2597,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
@@ -2632,10 +2626,10 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -2664,10 +2658,10 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>13</v>
@@ -2696,10 +2690,10 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2728,10 +2722,10 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -2757,13 +2751,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2789,13 +2783,13 @@
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2821,13 +2815,13 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2856,10 +2850,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -2888,10 +2882,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -2917,13 +2911,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -2949,13 +2943,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -2981,19 +2975,19 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -3013,19 +3007,19 @@
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -3045,19 +3039,19 @@
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -3077,19 +3071,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3109,19 +3103,19 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -3141,19 +3135,19 @@
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -3173,19 +3167,19 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3205,19 +3199,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3237,19 +3231,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3269,19 +3263,19 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3301,19 +3295,19 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3333,19 +3327,19 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3365,19 +3359,19 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3397,19 +3391,19 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3429,19 +3423,19 @@
         <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3461,19 +3455,19 @@
         <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3493,19 +3487,19 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3525,19 +3519,19 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3557,19 +3551,19 @@
         <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3589,19 +3583,19 @@
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3621,19 +3615,19 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3653,19 +3647,19 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3685,19 +3679,19 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3717,19 +3711,19 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3749,19 +3743,19 @@
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3781,19 +3775,19 @@
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3813,19 +3807,19 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3845,19 +3839,19 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3877,19 +3871,19 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3909,19 +3903,19 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -3941,19 +3935,19 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -3973,19 +3967,19 @@
         <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4005,19 +3999,19 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -4037,19 +4031,19 @@
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4069,19 +4063,19 @@
         <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4101,19 +4095,19 @@
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4133,19 +4127,19 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4165,19 +4159,19 @@
         <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4197,19 +4191,19 @@
         <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4229,19 +4223,19 @@
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4261,19 +4255,19 @@
         <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4293,19 +4287,19 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4325,19 +4319,19 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4357,19 +4351,19 @@
         <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4389,19 +4383,19 @@
         <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4421,19 +4415,19 @@
         <v>13</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4453,19 +4447,19 @@
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4485,19 +4479,19 @@
         <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4517,19 +4511,19 @@
         <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4549,19 +4543,19 @@
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4581,19 +4575,19 @@
         <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4613,19 +4607,19 @@
         <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4645,19 +4639,19 @@
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4677,19 +4671,19 @@
         <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4709,19 +4703,19 @@
         <v>6</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4741,19 +4735,19 @@
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4773,19 +4767,19 @@
         <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4805,19 +4799,19 @@
         <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4837,19 +4831,19 @@
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4869,19 +4863,19 @@
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4901,19 +4895,19 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4933,19 +4927,19 @@
         <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -4965,19 +4959,19 @@
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -4997,19 +4991,19 @@
         <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5029,19 +5023,19 @@
         <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5061,19 +5055,19 @@
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5093,19 +5087,19 @@
         <v>6</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5125,19 +5119,19 @@
         <v>13</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5157,19 +5151,19 @@
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5189,19 +5183,19 @@
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5221,19 +5215,19 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5253,19 +5247,19 @@
         <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5285,19 +5279,19 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5317,19 +5311,19 @@
         <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5349,19 +5343,19 @@
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5381,19 +5375,19 @@
         <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5413,19 +5407,19 @@
         <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5445,19 +5439,19 @@
         <v>13</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5477,19 +5471,19 @@
         <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5509,19 +5503,19 @@
         <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5541,19 +5535,19 @@
         <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5573,19 +5567,19 @@
         <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5605,19 +5599,19 @@
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5637,19 +5631,19 @@
         <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5669,19 +5663,19 @@
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5701,19 +5695,19 @@
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5733,19 +5727,19 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5765,19 +5759,19 @@
         <v>13</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5797,19 +5791,19 @@
         <v>16</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5829,19 +5823,19 @@
         <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5861,19 +5855,19 @@
         <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5893,19 +5887,19 @@
         <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5925,19 +5919,19 @@
         <v>6</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -5957,19 +5951,19 @@
         <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -5989,19 +5983,19 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6021,19 +6015,19 @@
         <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6053,19 +6047,19 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6085,19 +6079,19 @@
         <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6117,19 +6111,19 @@
         <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6149,19 +6143,19 @@
         <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6181,19 +6175,19 @@
         <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6213,19 +6207,19 @@
         <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6245,19 +6239,19 @@
         <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6277,19 +6271,19 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6309,19 +6303,19 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6341,19 +6335,19 @@
         <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6373,19 +6367,19 @@
         <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6405,19 +6399,19 @@
         <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6437,19 +6431,19 @@
         <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6469,19 +6463,19 @@
         <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6501,19 +6495,19 @@
         <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6533,19 +6527,19 @@
         <v>16</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6565,19 +6559,19 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6597,19 +6591,19 @@
         <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6629,19 +6623,19 @@
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6661,19 +6655,19 @@
         <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6693,19 +6687,19 @@
         <v>6</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6725,19 +6719,19 @@
         <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6757,19 +6751,19 @@
         <v>6</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6789,19 +6783,19 @@
         <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6821,19 +6815,19 @@
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6853,19 +6847,19 @@
         <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6885,19 +6879,19 @@
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6917,19 +6911,19 @@
         <v>13</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -6949,19 +6943,19 @@
         <v>6</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -6981,19 +6975,19 @@
         <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7013,19 +7007,19 @@
         <v>16</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7045,19 +7039,19 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7077,19 +7071,19 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7109,19 +7103,19 @@
         <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7141,19 +7135,19 @@
         <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7173,19 +7167,19 @@
         <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7205,19 +7199,19 @@
         <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7237,19 +7231,19 @@
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7269,19 +7263,19 @@
         <v>16</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7301,19 +7295,19 @@
         <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7333,19 +7327,19 @@
         <v>5</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7365,19 +7359,19 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7397,19 +7391,19 @@
         <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7429,19 +7423,19 @@
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7461,19 +7455,19 @@
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7493,19 +7487,19 @@
         <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7525,19 +7519,19 @@
         <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7557,19 +7551,19 @@
         <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7589,19 +7583,19 @@
         <v>7</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7621,19 +7615,19 @@
         <v>16</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7653,19 +7647,19 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7685,19 +7679,19 @@
         <v>16</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7717,19 +7711,19 @@
         <v>7</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7749,19 +7743,19 @@
         <v>16</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7781,19 +7775,19 @@
         <v>16</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7813,19 +7807,19 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7845,19 +7839,19 @@
         <v>7</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7877,19 +7871,19 @@
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7909,19 +7903,19 @@
         <v>6</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7941,19 +7935,19 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -7973,19 +7967,19 @@
         <v>16</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8005,19 +7999,19 @@
         <v>5</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8037,19 +8031,19 @@
         <v>6</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8069,19 +8063,19 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8101,19 +8095,19 @@
         <v>16</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8133,19 +8127,19 @@
         <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8165,19 +8159,19 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8197,19 +8191,19 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8229,19 +8223,19 @@
         <v>16</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8261,19 +8255,19 @@
         <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8293,19 +8287,19 @@
         <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8325,19 +8319,19 @@
         <v>1</v>
       </c>
       <c r="C183" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="F183" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E183" s="2" t="s">
+      <c r="G183" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8357,19 +8351,19 @@
         <v>4</v>
       </c>
       <c r="C184" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E184" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D184" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="F184" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8389,19 +8383,19 @@
         <v>3</v>
       </c>
       <c r="C185" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D185" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="F185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8421,19 +8415,19 @@
         <v>1</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8453,19 +8447,19 @@
         <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8485,19 +8479,19 @@
         <v>2</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D188" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="F188" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8517,19 +8511,19 @@
         <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8549,19 +8543,19 @@
         <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8581,19 +8575,19 @@
         <v>1</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8613,19 +8607,19 @@
         <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8645,19 +8639,19 @@
         <v>2</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8677,19 +8671,19 @@
         <v>2</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8709,19 +8703,19 @@
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8741,19 +8735,19 @@
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8773,19 +8767,19 @@
         <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8805,19 +8799,19 @@
         <v>1</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8837,19 +8831,19 @@
         <v>2</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8869,19 +8863,19 @@
         <v>1</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8901,19 +8895,19 @@
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8933,19 +8927,19 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -8965,19 +8959,19 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -8997,19 +8991,19 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9029,19 +9023,19 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9061,19 +9055,19 @@
         <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9093,19 +9087,19 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9125,19 +9119,19 @@
         <v>2</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9157,19 +9151,19 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9189,19 +9183,19 @@
         <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9221,19 +9215,19 @@
         <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9253,19 +9247,19 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9285,19 +9279,19 @@
         <v>3</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9317,19 +9311,19 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9349,19 +9343,19 @@
         <v>4</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9381,19 +9375,19 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9413,19 +9407,19 @@
         <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9445,19 +9439,19 @@
         <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9477,19 +9471,19 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9509,19 +9503,19 @@
         <v>1</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9541,19 +9535,19 @@
         <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9573,19 +9567,19 @@
         <v>8</v>
       </c>
       <c r="C222" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E222" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D222" s="2" t="s">
+      <c r="F222" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="E222" s="2" t="s">
+      <c r="G222" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G222" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9605,19 +9599,19 @@
         <v>10</v>
       </c>
       <c r="C223" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="F223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9637,19 +9631,19 @@
         <v>10</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9669,19 +9663,19 @@
         <v>8</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9701,19 +9695,19 @@
         <v>9</v>
       </c>
       <c r="C226" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D226" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="F226" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9733,19 +9727,19 @@
         <v>10</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9765,19 +9759,19 @@
         <v>9</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9797,19 +9791,19 @@
         <v>10</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9829,19 +9823,19 @@
         <v>10</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9861,19 +9855,19 @@
         <v>14</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="F231" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9893,19 +9887,19 @@
         <v>10</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9925,19 +9919,19 @@
         <v>10</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -9957,19 +9951,19 @@
         <v>14</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -9989,19 +9983,19 @@
         <v>10</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10021,19 +10015,19 @@
         <v>10</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10053,19 +10047,19 @@
         <v>8</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10085,19 +10079,19 @@
         <v>10</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10117,19 +10111,19 @@
         <v>10</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10149,19 +10143,19 @@
         <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10181,19 +10175,19 @@
         <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10213,19 +10207,19 @@
         <v>9</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10245,19 +10239,19 @@
         <v>10</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10277,19 +10271,19 @@
         <v>9</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10309,19 +10303,19 @@
         <v>10</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10341,19 +10335,19 @@
         <v>9</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10373,19 +10367,19 @@
         <v>8</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10405,19 +10399,19 @@
         <v>9</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10437,19 +10431,19 @@
         <v>9</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10469,19 +10463,19 @@
         <v>8</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10501,19 +10495,19 @@
         <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10533,19 +10527,19 @@
         <v>8</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10565,19 +10559,19 @@
         <v>9</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10597,19 +10591,19 @@
         <v>10</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10629,19 +10623,19 @@
         <v>10</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10661,19 +10655,19 @@
         <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10693,19 +10687,19 @@
         <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10725,19 +10719,19 @@
         <v>8</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10757,19 +10751,19 @@
         <v>10</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10789,19 +10783,19 @@
         <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10821,19 +10815,19 @@
         <v>14</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10853,19 +10847,19 @@
         <v>14</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10885,19 +10879,19 @@
         <v>10</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -10917,19 +10911,19 @@
         <v>9</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -10949,19 +10943,19 @@
         <v>9</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -10981,19 +10975,19 @@
         <v>10</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11013,19 +11007,19 @@
         <v>8</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11045,19 +11039,19 @@
         <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11077,19 +11071,19 @@
         <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11109,19 +11103,19 @@
         <v>14</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11141,19 +11135,19 @@
         <v>8</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11173,19 +11167,19 @@
         <v>10</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11205,19 +11199,19 @@
         <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11237,19 +11231,19 @@
         <v>8</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11269,19 +11263,19 @@
         <v>8</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11301,19 +11295,19 @@
         <v>8</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11333,19 +11327,19 @@
         <v>10</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11365,19 +11359,19 @@
         <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11397,19 +11391,19 @@
         <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11429,19 +11423,19 @@
         <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11461,19 +11455,19 @@
         <v>9</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11493,19 +11487,19 @@
         <v>8</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11525,19 +11519,19 @@
         <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11557,19 +11551,19 @@
         <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11589,19 +11583,19 @@
         <v>8</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11621,19 +11615,19 @@
         <v>9</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11653,19 +11647,19 @@
         <v>10</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11685,19 +11679,19 @@
         <v>8</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11717,19 +11711,19 @@
         <v>10</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11749,19 +11743,19 @@
         <v>8</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11781,19 +11775,19 @@
         <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11813,19 +11807,19 @@
         <v>9</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11845,19 +11839,19 @@
         <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11877,19 +11871,19 @@
         <v>14</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11909,19 +11903,19 @@
         <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -11941,19 +11935,19 @@
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -11973,19 +11967,19 @@
         <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12005,19 +11999,19 @@
         <v>14</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12037,19 +12031,19 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12069,19 +12063,19 @@
         <v>8</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12101,19 +12095,19 @@
         <v>8</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12133,19 +12127,19 @@
         <v>9</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12165,19 +12159,19 @@
         <v>14</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12197,19 +12191,19 @@
         <v>8</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12229,19 +12223,19 @@
         <v>8</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12261,19 +12255,19 @@
         <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12293,19 +12287,19 @@
         <v>8</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12325,19 +12319,19 @@
         <v>9</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12357,19 +12351,19 @@
         <v>9</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12389,19 +12383,19 @@
         <v>8</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12421,19 +12415,19 @@
         <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12453,19 +12447,19 @@
         <v>8</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12485,19 +12479,19 @@
         <v>8</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12517,19 +12511,19 @@
         <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12549,19 +12543,19 @@
         <v>14</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12581,19 +12575,19 @@
         <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12613,19 +12607,19 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12645,19 +12639,19 @@
         <v>8</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12677,19 +12671,19 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12709,19 +12703,19 @@
         <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12741,19 +12735,19 @@
         <v>9</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12773,19 +12767,19 @@
         <v>14</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12805,19 +12799,19 @@
         <v>8</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12837,19 +12831,19 @@
         <v>9</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12869,19 +12863,19 @@
         <v>14</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -12901,19 +12895,19 @@
         <v>8</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -12933,19 +12927,19 @@
         <v>9</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -12975,7 +12969,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12983,50 +12977,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -13048,21 +13042,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13071,7 +13065,7 @@
         <v>2024</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
